--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8E6FAE-A416-4247-BAF6-6797A930213F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5FF24F-2EAC-438C-82CF-444F23362636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily_Log" sheetId="1" r:id="rId1"/>
@@ -847,12 +847,6 @@
       <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="E15">
-        <v>2690</v>
-      </c>
-      <c r="F15">
-        <v>114</v>
-      </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
@@ -869,12 +863,6 @@
       </c>
       <c r="D16" t="s">
         <v>25</v>
-      </c>
-      <c r="F16">
-        <v>120</v>
-      </c>
-      <c r="G16">
-        <v>242</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5FF24F-2EAC-438C-82CF-444F23362636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E29CA-75A4-4451-BB71-4E0E8ABCFBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,6 +881,9 @@
       <c r="D17" t="s">
         <v>26</v>
       </c>
+      <c r="G17">
+        <v>242</v>
+      </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E29CA-75A4-4451-BB71-4E0E8ABCFBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC7697-FA04-4A4C-8F1C-31125DB8F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -626,6 +626,9 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
+      <c r="G2">
+        <v>245</v>
+      </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC7697-FA04-4A4C-8F1C-31125DB8F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57D0D9D-5BE4-41C8-AAC2-D1D9908D4B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily_Log" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -122,24 +122,6 @@
     <t>Reps</t>
   </si>
   <si>
-    <t>Legs</t>
-  </si>
-  <si>
-    <t>Goblet Squat</t>
-  </si>
-  <si>
-    <t>Romanian Deadlift</t>
-  </si>
-  <si>
-    <t>Leg Press</t>
-  </si>
-  <si>
-    <t>Leg Extension</t>
-  </si>
-  <si>
-    <t>Seated Leg Curl</t>
-  </si>
-  <si>
     <t>Calisthenics</t>
   </si>
   <si>
@@ -282,6 +264,39 @@
   </si>
   <si>
     <t>Keep filename exactly fitness_tracker.xlsx. Dashboard reads this file directly.</t>
+  </si>
+  <si>
+    <t>Back + Biceps + Walking</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>Seated Cable Row</t>
+  </si>
+  <si>
+    <t>Lat Pulldown</t>
+  </si>
+  <si>
+    <t>Straight Arm Cable Pulldown</t>
+  </si>
+  <si>
+    <t>Seated Iso-Lateral Row</t>
+  </si>
+  <si>
+    <t>Biceps</t>
+  </si>
+  <si>
+    <t>Dumbell Biceps Curl</t>
+  </si>
+  <si>
+    <t>Dumbbell Hammer Curl</t>
+  </si>
+  <si>
+    <t>Cable Curl</t>
+  </si>
+  <si>
+    <t>City Walk</t>
   </si>
 </sst>
 </file>
@@ -892,7 +907,21 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="1"/>
+      <c r="A18" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1"/>
@@ -2356,7 +2385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H500"/>
+  <dimension ref="A1:H495"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2395,13 +2424,13 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -2409,34 +2438,31 @@
       <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="F2">
-        <v>25</v>
-      </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -2447,74 +2473,74 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>90</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2537,13 +2563,16 @@
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2557,39 +2586,39 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -2600,45 +2629,45 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F11">
         <v>50</v>
@@ -2647,66 +2676,112 @@
         <v>3</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B15">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
@@ -4148,24 +4223,9 @@
     <row r="495" spans="1:1">
       <c r="A495" s="1"/>
     </row>
-    <row r="496" spans="1:1">
-      <c r="A496" s="1"/>
-    </row>
-    <row r="497" spans="1:1">
-      <c r="A497" s="1"/>
-    </row>
-    <row r="498" spans="1:1">
-      <c r="A498" s="1"/>
-    </row>
-    <row r="499" spans="1:1">
-      <c r="A499" s="1"/>
-    </row>
-    <row r="500" spans="1:1">
-      <c r="A500" s="1"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="D2:D495" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Chest,Back,Triceps,Shoulders,Abs/Core,Biceps,Calisthenics,Legs"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4198,19 +4258,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4224,7 +4284,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -4233,11 +4293,25 @@
         <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -5733,23 +5807,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>245</v>
@@ -5757,7 +5831,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <v>180</v>
@@ -5765,7 +5839,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>160</v>
@@ -5773,7 +5847,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -5797,7 +5871,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23">
       <c r="A1" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5805,72 +5879,72 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5881,10 +5955,10 @@
     </row>
     <row r="9" spans="1:4" ht="28">
       <c r="A9" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57D0D9D-5BE4-41C8-AAC2-D1D9908D4B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE3A9C-03BA-447D-B98B-A8B1358BDB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily_Log" sheetId="1" r:id="rId1"/>
@@ -919,6 +919,12 @@
       <c r="D18" t="s">
         <v>80</v>
       </c>
+      <c r="E18">
+        <v>2050</v>
+      </c>
+      <c r="F18">
+        <v>175</v>
+      </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE3A9C-03BA-447D-B98B-A8B1358BDB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D85080-27AF-45B3-99FF-6058DD336465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Chest + Triceps + Beginner Calisthenics</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Back + Biceps + Beginner Calisthenics</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>Cross-Trainer</t>
   </si>
   <si>
-    <t>0.4 mi</t>
-  </si>
-  <si>
     <t>Setting</t>
   </si>
   <si>
@@ -297,6 +291,93 @@
   </si>
   <si>
     <t>City Walk</t>
+  </si>
+  <si>
+    <t>Rest Day / Vacation (Teju Marriage)</t>
+  </si>
+  <si>
+    <t>Legs + Beginner Calisthenics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoulder + Tricep + Core </t>
+  </si>
+  <si>
+    <t>Shoulders</t>
+  </si>
+  <si>
+    <t>Legs</t>
+  </si>
+  <si>
+    <t>Body Weight Squats</t>
+  </si>
+  <si>
+    <t>Reverse Lunges</t>
+  </si>
+  <si>
+    <t>Dead Hangs</t>
+  </si>
+  <si>
+    <t>Leg Press</t>
+  </si>
+  <si>
+    <t>Seated Leg Curl</t>
+  </si>
+  <si>
+    <t>Leg Extensions</t>
+  </si>
+  <si>
+    <t>Dumbell Romanian Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hip Abductor - Out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calf Raises </t>
+  </si>
+  <si>
+    <t>Seated Dumbell Shoulder Press</t>
+  </si>
+  <si>
+    <t>Dumbell Lateral Raise</t>
+  </si>
+  <si>
+    <t>Rear Pec Deck</t>
+  </si>
+  <si>
+    <t>Cable Triceps Pushdown</t>
+  </si>
+  <si>
+    <t>Cable Overhead Triceps Extension</t>
+  </si>
+  <si>
+    <t>Single Arm Cable Tricep Pushdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest + Biceps + Beginner Calisthenics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cricket + Sprint Conditioning </t>
+  </si>
+  <si>
+    <t>Seated Iso-Lateral Chest Press</t>
+  </si>
+  <si>
+    <t>Plate-Loaded Incline Chest Press</t>
+  </si>
+  <si>
+    <t>Pec Fly</t>
+  </si>
+  <si>
+    <t>Dumbbell Curl</t>
+  </si>
+  <si>
+    <t>Hammer Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Curl </t>
   </si>
 </sst>
 </file>
@@ -644,9 +725,6 @@
       <c r="G2">
         <v>245</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1">
@@ -659,9 +737,6 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -676,10 +751,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -693,10 +765,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -710,10 +779,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -727,10 +793,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -744,10 +807,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
         <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -761,10 +824,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -778,10 +838,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -795,10 +852,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +866,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -829,10 +880,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -846,10 +894,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -863,10 +908,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -880,10 +922,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -897,13 +936,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17">
-        <v>242</v>
-      </c>
-      <c r="H17" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -917,53 +950,215 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18">
-        <v>2050</v>
-      </c>
-      <c r="F18">
-        <v>175</v>
-      </c>
-      <c r="H18" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="1"/>
+      <c r="A19" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="1"/>
+      <c r="A20" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="1"/>
+      <c r="A23" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="1"/>
+      <c r="A25" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="1"/>
+      <c r="A26" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26">
+        <v>2100</v>
+      </c>
+      <c r="F26">
+        <v>170</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27">
+        <v>3750</v>
+      </c>
+      <c r="F27">
+        <v>195</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="1"/>
+      <c r="A28" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28">
+        <v>2285</v>
+      </c>
+      <c r="F28">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="1"/>
+      <c r="A29" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29">
+        <v>2500</v>
+      </c>
+      <c r="F29">
+        <v>170</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="1"/>
+      <c r="A30" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1"/>
@@ -2391,7 +2586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H495"/>
+  <dimension ref="A1:H496"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2413,19 +2608,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2439,10 +2634,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -2462,10 +2657,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
         <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -2488,10 +2683,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>12.5</v>
@@ -2514,10 +2709,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>65</v>
@@ -2540,10 +2735,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
         <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
       </c>
       <c r="F6">
         <v>50</v>
@@ -2566,10 +2761,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -2592,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
         <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -2618,10 +2813,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F9">
         <v>60</v>
@@ -2644,10 +2839,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
         <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>83</v>
       </c>
       <c r="F10">
         <v>60</v>
@@ -2670,10 +2865,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11">
         <v>50</v>
@@ -2696,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F12">
         <v>25</v>
@@ -2722,10 +2917,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>15</v>
@@ -2748,10 +2943,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
         <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>88</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -2774,10 +2969,10 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>30</v>
@@ -2790,102 +2985,659 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="A16" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B16">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B19">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20">
+        <v>90</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21">
+        <v>85</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22">
+        <v>70</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B24">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24">
+        <v>130</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B25">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25">
+        <v>90</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26">
+        <v>30</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28">
+        <v>55</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29">
+        <v>50</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30">
+        <v>30</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B31">
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31">
+        <v>20</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B32">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32">
+        <v>70</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B33">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34">
+        <v>17.5</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B35">
+        <v>27</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35">
+        <v>60</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B36">
+        <v>27</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36">
+        <v>12.5</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B37">
+        <v>27</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B38">
+        <v>27</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38">
+        <v>40</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B39">
+        <v>27</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B40">
+        <v>27</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:8">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:8">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:8">
       <c r="A44" s="1"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:8">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:8">
       <c r="A46" s="1"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:8">
       <c r="A47" s="1"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:8">
       <c r="A48" s="1"/>
     </row>
     <row r="49" spans="1:1">
@@ -4229,9 +4981,12 @@
     <row r="495" spans="1:1">
       <c r="A495" s="1"/>
     </row>
+    <row r="496" spans="1:1">
+      <c r="A496" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D495" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="D2:D496" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Chest,Back,Triceps,Shoulders,Abs/Core,Biceps,Calisthenics,Legs"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4264,19 +5019,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4290,16 +5045,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2">
         <v>20</v>
-      </c>
-      <c r="F2">
-        <v>169</v>
-      </c>
-      <c r="G2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4313,7 +5062,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -5813,23 +6562,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>245</v>
@@ -5837,7 +6586,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>180</v>
@@ -5845,7 +6594,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>160</v>
@@ -5853,7 +6602,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -5877,7 +6626,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23">
       <c r="A1" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5885,72 +6634,72 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5961,10 +6710,10 @@
     </row>
     <row r="9" spans="1:4" ht="28">
       <c r="A9" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D85080-27AF-45B3-99FF-6058DD336465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463ABF0F-3501-4BD7-B855-F3FD52B6CED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily_Log" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="128">
   <si>
     <t>Date</t>
   </si>
@@ -378,6 +378,36 @@
   </si>
   <si>
     <t xml:space="preserve">Cable Curl </t>
+  </si>
+  <si>
+    <t>Active Recovery</t>
+  </si>
+  <si>
+    <t>Upper Body Strength + Calesthenics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cricket </t>
+  </si>
+  <si>
+    <t>Cardio</t>
+  </si>
+  <si>
+    <t>Incline Threadmill - 30m (7/2.7)</t>
+  </si>
+  <si>
+    <t>Machine shoulder press</t>
+  </si>
+  <si>
+    <t>DB Hammer Curl</t>
+  </si>
+  <si>
+    <t>Face pulls</t>
+  </si>
+  <si>
+    <t>Hip Adduction - In</t>
+  </si>
+  <si>
+    <t>Goblet Squats</t>
   </si>
 </sst>
 </file>
@@ -1159,12 +1189,61 @@
       <c r="B30">
         <v>29</v>
       </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30">
+        <v>1725</v>
+      </c>
+      <c r="F30">
+        <v>115</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="1"/>
+      <c r="A31" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31">
+        <v>2920</v>
+      </c>
+      <c r="F31">
+        <v>178</v>
+      </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="1"/>
+      <c r="A32" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32">
+        <v>2110</v>
+      </c>
+      <c r="F32">
+        <v>139</v>
+      </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1"/>
@@ -3617,75 +3696,462 @@
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="1"/>
+      <c r="A41" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B41">
+        <v>28</v>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="1"/>
+      <c r="A42" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B42">
+        <v>29</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="1"/>
+      <c r="A43" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B43">
+        <v>30</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43">
+        <v>60</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="1"/>
+      <c r="A44" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B44">
+        <v>30</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44">
+        <v>70</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="H44">
+        <v>12</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="1"/>
+      <c r="A45" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B45">
+        <v>30</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45">
+        <v>40</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="1"/>
+      <c r="A46" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46">
+        <v>12</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="1"/>
+      <c r="A47" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B47">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47">
+        <v>12.5</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>12</v>
+      </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1"/>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1"/>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="A48" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B48">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48">
+        <v>40</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B49">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" t="s">
+        <v>125</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B50">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B51">
+        <v>30</v>
+      </c>
+      <c r="C51">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>96</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B52">
+        <v>31</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" t="s">
+        <v>98</v>
+      </c>
+      <c r="F52">
+        <v>85</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B53">
+        <v>31</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F53">
+        <v>70</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B54">
+        <v>31</v>
+      </c>
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54">
+        <v>100</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B55">
+        <v>31</v>
+      </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F55">
+        <v>130</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B56">
+        <v>31</v>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" t="s">
+        <v>126</v>
+      </c>
+      <c r="F56">
+        <v>130</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B57">
+        <v>31</v>
+      </c>
+      <c r="C57">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" t="s">
+        <v>103</v>
+      </c>
+      <c r="F57">
+        <v>75</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B58">
+        <v>31</v>
+      </c>
+      <c r="C58">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" t="s">
+        <v>127</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1"/>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:8">
       <c r="A60" s="1"/>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:8">
       <c r="A61" s="1"/>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:8">
       <c r="A62" s="1"/>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:8">
       <c r="A63" s="1"/>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:8">
       <c r="A64" s="1"/>
     </row>
     <row r="65" spans="1:1">
@@ -5069,7 +5535,21 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B4">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1"/>
@@ -6548,6 +7028,11 @@
       <c r="A496" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D4" xr:uid="{0AFB1DB3-33C3-46FC-8D0B-BAD275B4E370}">
+      <formula1>"Chest,Back,Triceps,Shoulders,Abs/Core,Biceps,Calisthenics,Legs"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463ABF0F-3501-4BD7-B855-F3FD52B6CED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54470C4B-56DB-474A-B1AE-7366E3106993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily_Log" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="136">
   <si>
     <t>Date</t>
   </si>
@@ -408,6 +408,30 @@
   </si>
   <si>
     <t>Goblet Squats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest + Back + Core </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incline Cardio / Active Recovery </t>
+  </si>
+  <si>
+    <t>Incline DB Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest supported DB row </t>
+  </si>
+  <si>
+    <t>Pallof Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plank </t>
+  </si>
+  <si>
+    <t>7% , 2.7</t>
+  </si>
+  <si>
+    <t>Shoulder + Arms + Core</t>
   </si>
 </sst>
 </file>
@@ -417,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -432,6 +456,10 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF19D3FF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1244,53 +1272,118 @@
       <c r="F32">
         <v>139</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34">
+        <v>2215</v>
+      </c>
+      <c r="F34">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35">
+        <v>2630</v>
+      </c>
+      <c r="F35">
+        <v>129</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:8">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:8">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:8">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:8">
       <c r="A44" s="1"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:8">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:8">
       <c r="A46" s="1"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:8">
       <c r="A47" s="1"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:8">
       <c r="A48" s="1"/>
     </row>
     <row r="49" spans="1:1">
@@ -4137,69 +4230,250 @@
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="1"/>
+      <c r="A59" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B59">
+        <v>33</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" t="s">
+        <v>35</v>
+      </c>
+      <c r="F59">
+        <v>15</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>12</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="1"/>
+      <c r="A60" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B60">
+        <v>33</v>
+      </c>
+      <c r="C60">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60">
+        <v>17.5</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="H60">
+        <v>12</v>
+      </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="1"/>
+      <c r="A61" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B61">
+        <v>33</v>
+      </c>
+      <c r="C61">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>33</v>
+      </c>
+      <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61">
+        <v>75</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61">
+        <v>12</v>
+      </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="1"/>
+      <c r="A62" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B62">
+        <v>33</v>
+      </c>
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62">
+        <v>60</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+      <c r="H62">
+        <v>12</v>
+      </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="1"/>
+      <c r="A63" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B63">
+        <v>33</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63">
+        <v>15</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63">
+        <v>12</v>
+      </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="A64" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B64">
+        <v>33</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>40</v>
+      </c>
+      <c r="E64" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64">
+        <v>120</v>
+      </c>
+      <c r="G64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B65">
+        <v>33</v>
+      </c>
+      <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F65">
+        <v>40</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B66">
+        <v>33</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1"/>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:8">
       <c r="A68" s="1"/>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:8">
       <c r="A69" s="1"/>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:8">
       <c r="A70" s="1"/>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:8">
       <c r="A71" s="1"/>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:8">
       <c r="A72" s="1"/>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:8">
       <c r="A73" s="1"/>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:8">
       <c r="A74" s="1"/>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:8">
       <c r="A75" s="1"/>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:8">
       <c r="A76" s="1"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:8">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:8">
       <c r="A78" s="1"/>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:8">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:8">
       <c r="A80" s="1"/>
     </row>
     <row r="81" spans="1:1">
@@ -5552,10 +5826,44 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B5">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -7028,8 +7336,9 @@
       <c r="A496" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4" xr:uid="{0AFB1DB3-33C3-46FC-8D0B-BAD275B4E370}">
+    <dataValidation type="list" sqref="D4:D6" xr:uid="{0AFB1DB3-33C3-46FC-8D0B-BAD275B4E370}">
       <formula1>"Chest,Back,Triceps,Shoulders,Abs/Core,Biceps,Calisthenics,Legs"</formula1>
     </dataValidation>
   </dataValidations>

--- a/fitness_tracker.xlsx
+++ b/fitness_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsamv\Downloads\fitness_dashboard_github_upload\FitnessDashboard\transformation-dashboard-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54470C4B-56DB-474A-B1AE-7366E3106993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A8C173-AACF-465D-AF9A-08B5E6A8D3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,15 @@
     <sheet name="Settings" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Workout_Log!$A$1:$H$76</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="139">
   <si>
     <t>Date</t>
   </si>
@@ -432,6 +435,15 @@
   </si>
   <si>
     <t>Shoulder + Arms + Core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sick </t>
+  </si>
+  <si>
+    <t>Legs + Core + Beginner Calisthenics</t>
+  </si>
+  <si>
+    <t>Dumbell RDL</t>
   </si>
 </sst>
 </file>
@@ -1351,13 +1363,64 @@
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="1"/>
+      <c r="A37" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37">
+        <v>1600</v>
+      </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="1"/>
+      <c r="A38" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38">
+        <v>1400</v>
+      </c>
+      <c r="F38">
+        <v>90</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="1"/>
+      <c r="A39" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39">
+        <v>1950</v>
+      </c>
+      <c r="F39">
+        <v>130</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1"/>
@@ -4435,34 +4498,258 @@
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="1"/>
+      <c r="A67" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B67">
+        <v>38</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" t="s">
+        <v>138</v>
+      </c>
+      <c r="F67">
+        <v>20</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67">
+        <v>12</v>
+      </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="1"/>
+      <c r="A68" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B68">
+        <v>38</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68">
+        <v>75</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>12</v>
+      </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="1"/>
+      <c r="A69" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B69">
+        <v>38</v>
+      </c>
+      <c r="C69">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" t="s">
+        <v>97</v>
+      </c>
+      <c r="F69">
+        <v>110</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69">
+        <v>12</v>
+      </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="1"/>
+      <c r="A70" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B70">
+        <v>38</v>
+      </c>
+      <c r="C70">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" t="s">
+        <v>98</v>
+      </c>
+      <c r="F70">
+        <v>85</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70">
+        <v>12</v>
+      </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="1"/>
+      <c r="A71" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B71">
+        <v>38</v>
+      </c>
+      <c r="C71">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" t="s">
+        <v>103</v>
+      </c>
+      <c r="F71">
+        <v>75</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71">
+        <v>12</v>
+      </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="1"/>
+      <c r="A72" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B72">
+        <v>38</v>
+      </c>
+      <c r="C72">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F72">
+        <v>130</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="H72">
+        <v>12</v>
+      </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="1"/>
+      <c r="A73" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B73">
+        <v>38</v>
+      </c>
+      <c r="C73">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>40</v>
+      </c>
+      <c r="E73" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73">
+        <v>120</v>
+      </c>
+      <c r="G73">
+        <v>3</v>
+      </c>
+      <c r="H73">
+        <v>12</v>
+      </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="1"/>
+      <c r="A74" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B74">
+        <v>38</v>
+      </c>
+      <c r="C74">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" t="s">
+        <v>132</v>
+      </c>
+      <c r="F74">
+        <v>40</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="1"/>
+      <c r="A75" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B75">
+        <v>38</v>
+      </c>
+      <c r="C75">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" t="s">
+        <v>96</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>25</v>
+      </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="1"/>
+      <c r="A76" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B76">
+        <v>38</v>
+      </c>
+      <c r="C76">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>8</v>
+      </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1"/>
@@ -5725,6 +6012,7 @@
       <c r="A496" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H76" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D496" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Chest,Back,Triceps,Shoulders,Abs/Core,Biceps,Calisthenics,Legs"</formula1>
